--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1052,55 +1052,55 @@
         <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1052,55 +1052,55 @@
         <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R4" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
         <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2666,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>3.89</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.89</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,55 +2324,55 @@
         <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC3" t="n">
         <v>3.3</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>3.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -893,22 +893,22 @@
         <v>4.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="U3" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -920,25 +920,25 @@
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
         <v>2.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
         <v>1.75</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2348,13 +2348,13 @@
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
         <v>2.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AB12" t="n">
         <v>1.56</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="O14" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7</v>
+        <v>5.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="S12" t="n">
         <v>1.6</v>
@@ -2348,16 +2348,16 @@
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
         <v>2.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
         <v>4.3</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.46</v>
+        <v>4.03</v>
       </c>
       <c r="R14" t="n">
         <v>1.76</v>
@@ -2666,31 +2666,31 @@
         <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AA14" t="n">
         <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="AD14" t="n">
         <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>5.22</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7</v>
+        <v>5.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
         <v>1.6</v>
@@ -2354,13 +2354,13 @@
         <v>2.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AD12" t="n">
         <v>1.16</v>
@@ -2372,7 +2372,7 @@
         <v>1.97</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2633,22 +2633,22 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="P14" t="n">
         <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="T14" t="n">
         <v>2.13</v>
@@ -2657,28 +2657,28 @@
         <v>4.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
         <v>2.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AB14" t="n">
         <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="AD14" t="n">
         <v>1.06</v>
@@ -2690,7 +2690,7 @@
         <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.86</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>5.22</v>
+        <v>3.86</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>4.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.86</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.96</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>3.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.8</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2639,7 +2639,7 @@
         <v>2.77</v>
       </c>
       <c r="P14" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.8</v>
+        <v>5.22</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
         <v>2.38</v>
@@ -1085,7 +1085,7 @@
         <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
         <v>4.1</v>
@@ -1205,10 +1205,10 @@
         <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
         <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="n">
         <v>2.88</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2480,7 +2480,7 @@
         <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2321,7 +2321,7 @@
         <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>2.88</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="O3" t="n">
-        <v>3.98</v>
+        <v>3.42</v>
       </c>
       <c r="P3" t="n">
-        <v>5.35</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.12</v>
+        <v>3.98</v>
       </c>
       <c r="P4" t="n">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>2.4</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P14" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>3.98</v>
+        <v>3.12</v>
       </c>
       <c r="P4" t="n">
-        <v>5.35</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.12</v>
+        <v>3.98</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="O4" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O3" t="n">
         <v>3.12</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.71</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>5.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3.98</v>
+        <v>3.18</v>
       </c>
       <c r="P5" t="n">
-        <v>5.35</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.47</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="Q12" t="n">
         <v>2.88</v>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.53</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC3" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.98</v>
+        <v>3.12</v>
       </c>
       <c r="P4" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.18</v>
+        <v>3.98</v>
       </c>
       <c r="P5" t="n">
-        <v>3.8</v>
+        <v>5.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>1.84</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
         <v>2.4</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.98</v>
       </c>
       <c r="P3" t="n">
-        <v>3.8</v>
+        <v>5.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3.98</v>
+        <v>3.18</v>
       </c>
       <c r="P5" t="n">
-        <v>5.35</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>3.42</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.47</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>5.35</v>
+        <v>4.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
         <v>4.1</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.18</v>
+        <v>3.98</v>
       </c>
       <c r="P5" t="n">
-        <v>3.8</v>
+        <v>5.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="O8" t="n">
-        <v>3.42</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="Q12" t="n">
         <v>2.88</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P3" t="n">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC4" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>3.59</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>3.53</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4.16</v>
+        <v>3.52</v>
       </c>
       <c r="P9" t="n">
-        <v>11.9</v>
+        <v>6.63</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.84</v>
+        <v>3.37</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="P10" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="P14" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>1.72</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>5.35</v>
+        <v>4.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>3.59</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>3.53</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="O8" t="n">
-        <v>3.59</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>3.53</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.37</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>3.36</v>
+        <v>3.02</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>3.37</v>
       </c>
       <c r="O11" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>2.88</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -721,17 +721,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -786,14 +786,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46178.27083333334</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="P3" t="n">
-        <v>4.1</v>
+        <v>5.35</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>3.98</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>3.37</v>
       </c>
       <c r="O10" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="P10" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.37</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>3.36</v>
+        <v>3.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,25 +852,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="P3" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '12']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '30']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46178.3125</v>
@@ -1011,16 +1011,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1032,24 +1032,24 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="P4" t="n">
-        <v>4.1</v>
+        <v>5.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46178.3125</v>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1191,24 +1191,24 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.29</v>
+        <v>3.55</v>
       </c>
       <c r="Q5" t="n">
         <v>2.38</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46178.3125</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.59</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>3.53</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.59</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>3.53</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>3.42</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.37</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>3.36</v>
+        <v>3.02</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>3.37</v>
       </c>
       <c r="O11" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,112 +852,112 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AG3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['4', '12']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>['27', '30']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -966,25 +966,25 @@
         <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.23</v>
+        <v>2.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.7</v>
+        <v>0.59</v>
       </c>
       <c r="AS3" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="AT3" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46178.3125</v>
@@ -1011,28 +1011,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['4', '12']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '30']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="n">
         <v>9</v>
       </c>
-      <c r="AN4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>14</v>
-      </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.03</v>
+        <v>1.23</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="AT4" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46178.3125</v>
@@ -1170,19 +1170,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="O5" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.59</v>
+        <v>1.38</v>
       </c>
       <c r="AS5" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AT5" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46178.3125</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1841,10 +1841,10 @@
         <v>1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>6.63</v>
+        <v>5.75</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.37</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q12" t="n">
         <v>2.88</v>
@@ -2357,7 +2357,7 @@
         <v>2.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
         <v>4.15</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
         <v>2.68</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
         <v>3.8</v>
@@ -2675,7 +2675,7 @@
         <v>3.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
         <v>6.45</v>
@@ -2795,10 +2795,10 @@
         <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,19 +852,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,107 +884,107 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2</v>
-      </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.59</v>
+        <v>1.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AT3" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46178.3125</v>
@@ -1011,112 +1011,112 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AG4" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['4', '12']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['27', '30']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1125,25 +1125,25 @@
         <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.23</v>
+        <v>2.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.7</v>
+        <v>0.59</v>
       </c>
       <c r="AS4" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="AT4" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46178.3125</v>
@@ -1170,28 +1170,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.35</v>
+        <v>1.82</v>
       </c>
       <c r="O5" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['4', '12']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '30']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO5" t="n">
         <v>9</v>
       </c>
-      <c r="AN5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>14</v>
-      </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.03</v>
+        <v>1.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="AT5" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46178.3125</v>
@@ -1329,45 +1329,45 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '53']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1488,45 +1488,45 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '45']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '74']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1668,14 +1668,14 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1740,14 +1740,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1815,26 +1815,26 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1899,14 +1899,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>['18', '88']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
@@ -1917,28 +1917,28 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46178.60416666666</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -852,28 +852,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="P3" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['4', '12']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '30']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO3" t="n">
         <v>9</v>
       </c>
-      <c r="AN3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>14</v>
-      </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.03</v>
+        <v>1.23</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46178.3125</v>
@@ -1170,28 +1170,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="P5" t="n">
-        <v>4.1</v>
+        <v>5.35</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['4', '12']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['27', '30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP5" t="n">
         <v>8</v>
       </c>
-      <c r="AO5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>1.23</v>
+        <v>2.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AS5" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AT5" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46178.3125</v>
@@ -1329,22 +1329,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '45']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['1', '53']</t>
+          <t>['8', '74']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN6" t="n">
         <v>5</v>
       </c>
-      <c r="AN6" t="n">
-        <v>3</v>
-      </c>
       <c r="AO6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="AS6" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="AT6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>['7', '45']</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>['8', '74']</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>5</v>
-      </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.86</v>
+        <v>0.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="AT7" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1647,45 +1647,45 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '53']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP8" t="n">
         <v>7</v>
       </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>2.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AT8" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46178.66666666666</v>
@@ -2133,26 +2133,26 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '23', '59']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
@@ -2235,28 +2235,28 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46178.66666666666</v>

--- a/jogos_2026-06-05.xlsx
+++ b/jogos_2026-06-05.xlsx
@@ -1011,19 +1011,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN4" t="n">
         <v>3</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2</v>
-      </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.59</v>
+        <v>1.38</v>
       </c>
       <c r="AS4" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AT4" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46178.3125</v>
@@ -1170,19 +1170,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>3.98</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>5.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP5" t="n">
         <v>3</v>
       </c>
-      <c r="AO5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.38</v>
+        <v>0.59</v>
       </c>
       <c r="AS5" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="AT5" t="n">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46178.3125</v>
@@ -1329,22 +1329,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>['7', '45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['8', '74']</t>
+          <t>['1', '53']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="AT6" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1488,45 +1488,45 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['7', '45']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '74']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.53</v>
+        <v>1.25</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.83</v>
+        <v>1.86</v>
       </c>
       <c r="AS7" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>['1', '53']</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>3</v>
-      </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.63</v>
+        <v>2.53</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="AS8" t="n">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="AT8" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46178.54166666666</v>
@@ -1965,28 +1965,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '23', '59']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN10" t="n">
         <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.68</v>
+        <v>0.99</v>
       </c>
       <c r="AS10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AT10" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46178.66666666666</v>
@@ -2124,139 +2124,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P11" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['14', '23', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.99</v>
+        <v>1.68</v>
       </c>
       <c r="AS11" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AT11" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46178.66666666666</v>
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2357,7 +2357,7 @@
         <v>2.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
         <v>4.15</v>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '90+5']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
@@ -2394,28 +2394,28 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46178.83333333334</v>
